--- a/Data/Velavan Clinic Expense.xlsx
+++ b/Data/Velavan Clinic Expense.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d772b42a7a1256b2/Desktop/Business/TSK Constructions/Projects/Building Construction/Vellavan Site Saravanampatty/Accounts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="535" documentId="13_ncr:1_{A897D8FB-91AB-4CE7-9AEF-C0B79DED4CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{052D7888-C190-44A6-9DE5-DB4A65BC0534}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{7E2FB590-B210-4FBC-B7AC-AB3EBA36E56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6929C9EF-C56A-4EFA-BF8B-8117BAC389C3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="7" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="299">
   <si>
     <t>DATE</t>
   </si>
@@ -845,6 +845,102 @@
   </si>
   <si>
     <t>Advance</t>
+  </si>
+  <si>
+    <t>Cutting Machine for mason Team - Nithish</t>
+  </si>
+  <si>
+    <t>Madhappan lab Adv</t>
+  </si>
+  <si>
+    <t>FF Lindel stage payment</t>
+  </si>
+  <si>
+    <t>Lindel work adv</t>
+  </si>
+  <si>
+    <t>AK Steels</t>
+  </si>
+  <si>
+    <t>Vel Brick</t>
+  </si>
+  <si>
+    <t>Madhapan Adv</t>
+  </si>
+  <si>
+    <t>Lindel Advance Ayyapan</t>
+  </si>
+  <si>
+    <t>Madhappan Xtra</t>
+  </si>
+  <si>
+    <t>AK Steels - Acc - 1.2L Chq - 1.8 L Acc - 6K</t>
+  </si>
+  <si>
+    <t>Paid to Suresh</t>
+  </si>
+  <si>
+    <t>Labour Auto To Kovilpalayam Cleaning new site</t>
+  </si>
+  <si>
+    <t>Ayyapan advance FF Roof</t>
+  </si>
+  <si>
+    <t>Auto From Kovilpalayam to DR site</t>
+  </si>
+  <si>
+    <t>FF Roof Adv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Tea </t>
+  </si>
+  <si>
+    <t>Kovilpalayam Site cleaning Work</t>
+  </si>
+  <si>
+    <t>Selvam Material Purchase</t>
+  </si>
+  <si>
+    <t>Paid selvam 500 ,100 bal with Selvam</t>
+  </si>
+  <si>
+    <t>Green Net Purchase</t>
+  </si>
+  <si>
+    <t>Green Net Porter</t>
+  </si>
+  <si>
+    <t>Cement Unloading Tea</t>
+  </si>
+  <si>
+    <t>150 Bags Cement Purchase</t>
+  </si>
+  <si>
+    <t>Site Camera Recharge</t>
+  </si>
+  <si>
+    <t>Lunch Concrete Gang</t>
+  </si>
+  <si>
+    <t>Concrete Lunch Mason</t>
+  </si>
+  <si>
+    <t>Concrete Team Lift Fixing</t>
+  </si>
+  <si>
+    <t>Mason Lab</t>
+  </si>
+  <si>
+    <t>Roof Pipe Work</t>
+  </si>
+  <si>
+    <t>Roof Adv</t>
+  </si>
+  <si>
+    <t>FF roof Concrete</t>
+  </si>
+  <si>
+    <t>Petrol Mani</t>
   </si>
 </sst>
 </file>
@@ -908,7 +1004,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -941,6 +1037,17 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -980,7 +1087,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1371,13 +1478,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TAMIL" refreshedDate="46148.548349537035" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="238" xr:uid="{ECDDBE9B-8132-48D6-AEC8-4A5EB49DBA77}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="TAMIL" refreshedDate="46178.669334953702" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="279" xr:uid="{ECDDBE9B-8132-48D6-AEC8-4A5EB49DBA77}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:D1009" sheet="Expenses"/>
+    <worksheetSource ref="A1:D1008" sheet="Expenses"/>
   </cacheSource>
   <cacheFields count="4">
     <cacheField name="DATE" numFmtId="164">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-11-09T00:00:00" maxDate="2026-05-05T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2025-04-06T00:00:00" maxDate="2026-06-24T00:00:00"/>
     </cacheField>
     <cacheField name="TYPE OF EXPENSE" numFmtId="0">
       <sharedItems containsBlank="1" count="26">
@@ -1410,7 +1517,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="AMOUNT" numFmtId="165">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="30" maxValue="200000"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="30" maxValue="306000"/>
     </cacheField>
     <cacheField name="DESCRIPTION" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -1425,7 +1532,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="238">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="279">
   <r>
     <d v="2025-11-30T00:00:00"/>
     <x v="0"/>
@@ -2827,7 +2934,7 @@
   <r>
     <d v="2026-05-02T00:00:00"/>
     <x v="4"/>
-    <n v="120200"/>
+    <n v="120000"/>
     <s v="Vel brick 10000 nos"/>
   </r>
   <r>
@@ -2849,6 +2956,252 @@
     <s v="Tamil Karthi"/>
   </r>
   <r>
+    <d v="2025-04-06T00:00:00"/>
+    <x v="11"/>
+    <n v="10000"/>
+    <s v="Advance roof pending amt"/>
+  </r>
+  <r>
+    <d v="2026-04-06T00:00:00"/>
+    <x v="5"/>
+    <n v="10000"/>
+    <s v="Madhappan adv amount"/>
+  </r>
+  <r>
+    <d v="2026-05-07T00:00:00"/>
+    <x v="6"/>
+    <n v="1128"/>
+    <s v="Lab Tea"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="5"/>
+    <n v="54225"/>
+    <s v="Mason Lab Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="5"/>
+    <n v="500"/>
+    <s v="Madhappan Extra"/>
+  </r>
+  <r>
+    <d v="2026-05-09T00:00:00"/>
+    <x v="11"/>
+    <n v="20000"/>
+    <s v="Advance"/>
+  </r>
+  <r>
+    <d v="2026-05-11T00:00:00"/>
+    <x v="16"/>
+    <n v="100"/>
+    <s v="Cutting Machine for mason Team - Nithish"/>
+  </r>
+  <r>
+    <d v="2026-05-13T00:00:00"/>
+    <x v="5"/>
+    <n v="5000"/>
+    <s v="Madhappan lab Adv"/>
+  </r>
+  <r>
+    <d v="2026-05-14T00:00:00"/>
+    <x v="6"/>
+    <n v="928"/>
+    <s v="Lab Tea"/>
+  </r>
+  <r>
+    <d v="2026-05-16T00:00:00"/>
+    <x v="5"/>
+    <n v="36750"/>
+    <s v="Madhappan lab payment"/>
+  </r>
+  <r>
+    <d v="2026-05-16T00:00:00"/>
+    <x v="5"/>
+    <n v="500"/>
+    <s v="Madhappan Extra"/>
+  </r>
+  <r>
+    <d v="2026-05-16T00:00:00"/>
+    <x v="11"/>
+    <n v="30000"/>
+    <s v="Lindel work adv"/>
+  </r>
+  <r>
+    <d v="2026-05-16T00:00:00"/>
+    <x v="4"/>
+    <n v="200000"/>
+    <s v="AK Steels"/>
+  </r>
+  <r>
+    <d v="2026-05-16T00:00:00"/>
+    <x v="4"/>
+    <n v="60000"/>
+    <s v="Vel Brick"/>
+  </r>
+  <r>
+    <d v="2026-05-16T00:00:00"/>
+    <x v="18"/>
+    <n v="2000"/>
+    <s v="Car Diesel"/>
+  </r>
+  <r>
+    <d v="2026-05-20T00:00:00"/>
+    <x v="18"/>
+    <n v="1000"/>
+    <s v="Car Diesel"/>
+  </r>
+  <r>
+    <d v="2026-05-20T00:00:00"/>
+    <x v="5"/>
+    <n v="5000"/>
+    <s v="Madhapan Adv"/>
+  </r>
+  <r>
+    <d v="2026-05-20T00:00:00"/>
+    <x v="11"/>
+    <n v="7000"/>
+    <s v="Lindel Advance Ayyapan"/>
+  </r>
+  <r>
+    <d v="2026-05-23T00:00:00"/>
+    <x v="5"/>
+    <n v="43300"/>
+    <s v="Madhappan lab payment"/>
+  </r>
+  <r>
+    <d v="2026-05-23T00:00:00"/>
+    <x v="5"/>
+    <n v="550"/>
+    <s v="Madhappan Xtra"/>
+  </r>
+  <r>
+    <d v="2026-06-23T00:00:00"/>
+    <x v="4"/>
+    <n v="306000"/>
+    <s v="AK Steels - Acc - 1.2L Chq - 1.8 L Acc - 6K"/>
+  </r>
+  <r>
+    <d v="2026-06-23T00:00:00"/>
+    <x v="6"/>
+    <n v="496"/>
+    <s v="Lab Tea "/>
+  </r>
+  <r>
+    <d v="2026-05-26T00:00:00"/>
+    <x v="1"/>
+    <n v="5000"/>
+    <s v="Paid to Suresh"/>
+  </r>
+  <r>
+    <d v="2026-05-27T00:00:00"/>
+    <x v="15"/>
+    <n v="200"/>
+    <s v="Labour Auto To Kovilpalayam Cleaning new site"/>
+  </r>
+  <r>
+    <d v="2026-05-27T00:00:00"/>
+    <x v="11"/>
+    <n v="20000"/>
+    <s v="Ayyapan advance FF Roof"/>
+  </r>
+  <r>
+    <d v="2026-05-27T00:00:00"/>
+    <x v="15"/>
+    <n v="210"/>
+    <s v="Auto From Kovilpalayam to DR site"/>
+  </r>
+  <r>
+    <d v="2026-05-28T00:00:00"/>
+    <x v="18"/>
+    <n v="2000"/>
+    <s v="Car Diesel"/>
+  </r>
+  <r>
+    <d v="2026-05-30T00:00:00"/>
+    <x v="5"/>
+    <n v="18150"/>
+    <s v="Mason Lab Payment"/>
+  </r>
+  <r>
+    <d v="2026-05-30T00:00:00"/>
+    <x v="5"/>
+    <n v="2250"/>
+    <s v="Kovilpalayam Site cleaning Work"/>
+  </r>
+  <r>
+    <d v="2026-05-30T00:00:00"/>
+    <x v="11"/>
+    <n v="25000"/>
+    <s v="FF Roof Adv"/>
+  </r>
+  <r>
+    <d v="2026-05-30T00:00:00"/>
+    <x v="4"/>
+    <n v="16250"/>
+    <s v="Chakra cement payment"/>
+  </r>
+  <r>
+    <d v="2026-06-01T00:00:00"/>
+    <x v="18"/>
+    <n v="2000"/>
+    <s v="Car Diesel"/>
+  </r>
+  <r>
+    <d v="2026-06-04T00:00:00"/>
+    <x v="6"/>
+    <n v="300"/>
+    <s v="Lab Tea"/>
+  </r>
+  <r>
+    <d v="2026-06-04T00:00:00"/>
+    <x v="0"/>
+    <n v="400"/>
+    <s v="Selvam Material Purchase"/>
+  </r>
+  <r>
+    <d v="2026-06-04T00:00:00"/>
+    <x v="0"/>
+    <n v="100"/>
+    <s v="Paid selvam 500 ,100 bal with Selvam"/>
+  </r>
+  <r>
+    <d v="2026-06-04T00:00:00"/>
+    <x v="0"/>
+    <n v="1900"/>
+    <s v="Green Net Purchase"/>
+  </r>
+  <r>
+    <d v="2026-06-04T00:00:00"/>
+    <x v="7"/>
+    <n v="130"/>
+    <s v="Green Net Porter"/>
+  </r>
+  <r>
+    <d v="2026-06-04T00:00:00"/>
+    <x v="4"/>
+    <n v="46950"/>
+    <s v="150 Bags Cement Purchase"/>
+  </r>
+  <r>
+    <d v="2026-06-04T00:00:00"/>
+    <x v="0"/>
+    <n v="50"/>
+    <s v="Cement Unloading Tea"/>
+  </r>
+  <r>
+    <d v="2026-06-05T00:00:00"/>
+    <x v="0"/>
+    <n v="500"/>
+    <s v="Pooja Items for Concrete Nithish"/>
+  </r>
+  <r>
+    <d v="2026-06-05T00:00:00"/>
+    <x v="0"/>
+    <n v="149"/>
+    <s v="Site Camera Recharge"/>
+  </r>
+  <r>
     <m/>
     <x v="19"/>
     <m/>
@@ -2858,109 +3211,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{123E7EF1-D634-4326-8B1F-206D3919FDCB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
-  <location ref="G3:H8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="27">
-        <item h="1" x="4"/>
-        <item h="1" x="17"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="7"/>
-        <item h="1" m="1" x="20"/>
-        <item h="1" x="0"/>
-        <item h="1" x="19"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item h="1" x="6"/>
-        <item h="1" m="1" x="21"/>
-        <item x="9"/>
-        <item h="1" x="16"/>
-        <item h="1" x="13"/>
-        <item h="1" m="1" x="22"/>
-        <item h="1" x="15"/>
-        <item h="1" m="1" x="23"/>
-        <item h="1" m="1" x="24"/>
-        <item h="1" x="10"/>
-        <item h="1" m="1" x="25"/>
-        <item h="1" x="1"/>
-        <item h="1" x="8"/>
-        <item h="1" x="12"/>
-        <item h="1" x="14"/>
-        <item h="1" x="18"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total_Amount" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="5">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="4">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25AC62C7-A7F3-4225-A13E-8201E9F5861E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{25AC62C7-A7F3-4225-A13E-8201E9F5861E}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="D3:E7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -3022,27 +3273,27 @@
     <dataField name="Total_Amount" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="10">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="4">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -3058,8 +3309,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FC8C9A3-14B4-46FA-8D51-AAF7A0B6E9CA}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="A3:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -3169,27 +3420,27 @@
     <dataField name="Total_Amount" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="15">
+    <format dxfId="10">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="9">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -3205,8 +3456,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F3CF52-2B38-440E-A2E0-E3EBDEB38030}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4F3CF52-2B38-440E-A2E0-E3EBDEB38030}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
   <location ref="J3:K4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField showAll="0"/>
@@ -3248,6 +3499,111 @@
     <field x="1"/>
   </rowFields>
   <rowItems count="1">
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total_Amount" fld="2" baseField="0" baseItem="0" numFmtId="8"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="15">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{123E7EF1-D634-4326-8B1F-206D3919FDCB}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Expense">
+  <location ref="G3:H9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="27">
+        <item h="1" x="4"/>
+        <item h="1" x="17"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="7"/>
+        <item h="1" m="1" x="20"/>
+        <item h="1" x="0"/>
+        <item h="1" x="19"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item h="1" x="6"/>
+        <item h="1" m="1" x="21"/>
+        <item x="9"/>
+        <item h="1" x="16"/>
+        <item h="1" x="13"/>
+        <item h="1" m="1" x="22"/>
+        <item h="1" x="15"/>
+        <item h="1" m="1" x="23"/>
+        <item h="1" m="1" x="24"/>
+        <item x="10"/>
+        <item h="1" m="1" x="25"/>
+        <item h="1" x="1"/>
+        <item h="1" x="8"/>
+        <item h="1" x="12"/>
+        <item h="1" x="14"/>
+        <item h="1" x="18"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -3609,7 +3965,7 @@
       </c>
       <c r="K1" s="8">
         <f>SUM(B2:B201)</f>
-        <v>4811800</v>
+        <v>5811800</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -3783,7 +4139,7 @@
       </c>
       <c r="K8" s="8">
         <f>K1</f>
-        <v>4811800</v>
+        <v>5811800</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -3812,7 +4168,7 @@
       </c>
       <c r="K9" s="8">
         <f>K6-K8</f>
-        <v>9188200</v>
+        <v>8188200</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -3838,12 +4194,24 @@
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="A11" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="G11" s="9"/>
       <c r="H11" s="8"/>
     </row>
@@ -4057,7 +4425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}">
-  <dimension ref="A1:L307"/>
+  <dimension ref="A1:L306"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="5" bestFit="1" customWidth="1"/>
@@ -4092,7 +4460,7 @@
       </c>
       <c r="J1" s="7">
         <f>'Payment Received'!K1</f>
-        <v>4811800</v>
+        <v>5811800</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -4112,8 +4480,8 @@
         <v>7</v>
       </c>
       <c r="J2" s="7">
-        <f>SUM(C2:C510)</f>
-        <v>4563908</v>
+        <f>SUM(C2:C509)</f>
+        <v>5602571</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -4134,7 +4502,7 @@
       </c>
       <c r="J3" s="7">
         <f>J1-J2</f>
-        <v>247892</v>
+        <v>209229</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -7396,7 +7764,7 @@
         <v>23</v>
       </c>
       <c r="C235" s="7">
-        <v>120200</v>
+        <v>120000</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>262</v>
@@ -7490,13 +7858,13 @@
       <c r="A242" s="4">
         <v>46151</v>
       </c>
-      <c r="B242" s="27" t="s">
+      <c r="B242" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C242" s="7">
         <v>54225</v>
       </c>
-      <c r="D242" s="27" t="s">
+      <c r="D242" s="1" t="s">
         <v>172</v>
       </c>
     </row>
@@ -7504,13 +7872,13 @@
       <c r="A243" s="4">
         <v>46151</v>
       </c>
-      <c r="B243" s="27" t="s">
+      <c r="B243" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C243" s="7">
         <v>500</v>
       </c>
-      <c r="D243" s="27" t="s">
+      <c r="D243" s="1" t="s">
         <v>257</v>
       </c>
     </row>
@@ -7518,18 +7886,648 @@
       <c r="A244" s="4">
         <v>46151</v>
       </c>
-      <c r="B244" s="27" t="s">
+      <c r="B244" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C244" s="7">
         <v>20000</v>
       </c>
-      <c r="D244" s="27" t="s">
+      <c r="D244" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="307" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F307" s="8"/>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A245" s="4">
+        <v>46153</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C245" s="7">
+        <v>100</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A246" s="4">
+        <v>46155</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C246" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A247" s="4">
+        <v>46156</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C247" s="7">
+        <v>928</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A248" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C248" s="7">
+        <v>36750</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A249" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C249" s="7">
+        <v>500</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A250" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C250" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A251" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C251" s="7">
+        <v>200000</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A252" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C252" s="7">
+        <v>60000</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A253" s="4">
+        <v>46158</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C253" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A254" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C254" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A255" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C255" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A256" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C256" s="7">
+        <v>7000</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A257" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C257" s="7">
+        <v>43300</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A258" s="4">
+        <v>46165</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C258" s="7">
+        <v>550</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A259" s="4">
+        <v>46196</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C259" s="7">
+        <v>306000</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A260" s="4">
+        <v>46196</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C260" s="7">
+        <v>496</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A261" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C261" s="7">
+        <v>5000</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A262" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C262" s="7">
+        <v>200</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A263" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C263" s="7">
+        <v>20000</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A264" s="4">
+        <v>46169</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C264" s="7">
+        <v>210</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A265" s="4">
+        <v>46170</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C265" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A266" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C266" s="7">
+        <v>18150</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A267" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C267" s="7">
+        <v>2250</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A268" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C268" s="7">
+        <v>25000</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A269" s="4">
+        <v>46172</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C269" s="7">
+        <v>16250</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A270" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C270" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A271" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C271" s="7">
+        <v>2000</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A272" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C272" s="7">
+        <v>300</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A273" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C273" s="7">
+        <v>400</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A274" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C274" s="7">
+        <v>100</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A275" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C275" s="7">
+        <v>1900</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A276" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C276" s="7">
+        <v>130</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A277" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C277" s="7">
+        <v>46950</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" s="4">
+        <v>46177</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C278" s="7">
+        <v>50</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A279" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C279" s="7">
+        <v>149</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C280" s="7">
+        <v>1500</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C281" s="7">
+        <v>400</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" s="4">
+        <v>46178</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C282" s="7">
+        <v>200</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A283" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C283" s="7">
+        <v>21900</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A284" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C284" s="7">
+        <v>100</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A285" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C285" s="7">
+        <v>6000</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A286" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C286" s="7">
+        <v>100000</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A287" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C287" s="7">
+        <v>28000</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A288" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C288" s="7">
+        <v>39000</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A289" s="5">
+        <v>46179</v>
+      </c>
+      <c r="B289" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C289" s="8">
+        <v>100</v>
+      </c>
+      <c r="D289" s="27" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="306" spans="6:6" x14ac:dyDescent="0.35">
+      <c r="F306" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D85" xr:uid="{E716AC5E-A74E-4151-8738-1C2F14C945B6}"/>
@@ -7721,7 +8719,7 @@
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
@@ -7769,13 +8767,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="19">
-        <v>2627400</v>
+        <v>3256400</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="19">
-        <v>2627400</v>
+        <v>3256400</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>10</v>
@@ -7805,7 +8803,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="19">
-        <v>520940</v>
+        <v>697165</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -7825,7 +8823,7 @@
         <v>27</v>
       </c>
       <c r="H6" s="19">
-        <v>581775</v>
+        <v>693775</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -7839,7 +8837,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="20">
-        <v>2649460</v>
+        <v>3278460</v>
       </c>
       <c r="G7" s="15" t="s">
         <v>31</v>
@@ -7853,13 +8851,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="19">
-        <v>3600</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="20">
-        <v>1456015</v>
+        <v>3730</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="19">
+        <v>10000</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -7867,7 +8865,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="19">
-        <v>83826</v>
+        <v>86925</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="20">
+        <v>1754240</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -7875,7 +8879,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="19">
-        <v>520940</v>
+        <v>697165</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
@@ -7883,7 +8887,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="19">
-        <v>581775</v>
+        <v>693775</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -7891,7 +8895,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="19">
-        <v>11354</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -7907,7 +8911,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="19">
-        <v>9990</v>
+        <v>10090</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -7923,7 +8927,7 @@
         <v>37</v>
       </c>
       <c r="B16" s="19">
-        <v>3360</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -7939,7 +8943,7 @@
         <v>66</v>
       </c>
       <c r="B18" s="19">
-        <v>10500</v>
+        <v>15500</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -7971,7 +8975,7 @@
         <v>245</v>
       </c>
       <c r="B22" s="19">
-        <v>6000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -7979,7 +8983,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="20">
-        <v>4468055</v>
+        <v>5403871</v>
       </c>
     </row>
   </sheetData>
